--- a/emergency_report_forms/004_military_operations_incident_report_form--emergency_report_forms.xlsx
+++ b/emergency_report_forms/004_military_operations_incident_report_form--emergency_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1487,17 +1487,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>report_by_choices</t>
+          <t>incident_level_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>jane_doe</t>
+          <t>level_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jane Doe</t>
+          <t>Level 1</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>level_1</t>
+          <t>level_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Level 2</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>level_2</t>
+          <t>level_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
     </row>
@@ -1543,29 +1543,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>level_3</t>
+          <t>level_4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>incident_level_choices</t>
+          <t>incident_status_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>level_4</t>
+          <t>status_1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Level 4</t>
+          <t>Status 1</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>status_1</t>
+          <t>status_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Status 1</t>
+          <t>Status 2</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>status_2</t>
+          <t>status_3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Status 2</t>
+          <t>Status 3</t>
         </is>
       </c>
     </row>
@@ -1611,29 +1611,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>status_3</t>
+          <t>status_4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Status 3</t>
+          <t>Status 4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>incident_status_choices</t>
+          <t>incident_nature_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>status_4</t>
+          <t>nature_1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Status 4</t>
+          <t>Nature 1</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nature_1</t>
+          <t>nature_2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nature 1</t>
+          <t>Nature 2</t>
         </is>
       </c>
     </row>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nature_2</t>
+          <t>nature_3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nature 2</t>
+          <t>Nature 3</t>
         </is>
       </c>
     </row>
@@ -1679,29 +1679,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nature_3</t>
+          <t>nature_4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nature 3</t>
+          <t>Nature 4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>incident_nature_choices</t>
+          <t>incident_severity_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nature_4</t>
+          <t>severity_1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nature 4</t>
+          <t>Severity 1</t>
         </is>
       </c>
     </row>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>severity_1</t>
+          <t>severity_2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Severity 1</t>
+          <t>Severity 2</t>
         </is>
       </c>
     </row>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>severity_2</t>
+          <t>severity_3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Severity 2</t>
+          <t>Severity 3</t>
         </is>
       </c>
     </row>
@@ -1747,29 +1747,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>severity_3</t>
+          <t>severity_4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Severity 3</t>
+          <t>Severity 4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>incident_severity_choices</t>
+          <t>incident_priority_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>severity_4</t>
+          <t>priority_1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Severity 4</t>
+          <t>Priority 1</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>priority_1</t>
+          <t>priority_2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Priority 1</t>
+          <t>Priority 2</t>
         </is>
       </c>
     </row>
@@ -1798,12 +1798,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>priority_2</t>
+          <t>priority_3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Priority 2</t>
+          <t>Priority 3</t>
         </is>
       </c>
     </row>
@@ -1815,27 +1815,10 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>priority_3</t>
+          <t>priority_4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
-        <is>
-          <t>Priority 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>incident_priority_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>priority_4</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
         <is>
           <t>Priority 4</t>
         </is>
